--- a/output/2026-09-13_20_Croazia_Primorsko-goranska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-13_20_Croazia_Primorsko-goranska_Depolverazione_Trattamento_aria.xlsx
@@ -494,10 +494,9 @@
           <t>+385 51 818 626</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Confermato tramite fonti multiple (tvrtke.hr, ekvarner.info, sito ufficiale rgv.hr): produttore/distributore di elementi di ventilazione industriale, ventilatori di trasporto, filtri, silos, cicloni, cabine insonorizzate e sistemi di otprasivanje (depolverazione). Attivo dal 1995. Fit diretto e forte col settore target. Email generica non reperita, lasciata vuota.</t>
+          <t>Confermato tramite fonti multiple (tvrtke.hr, ekvarner.info, sito ufficiale rgv.hr): produttore/distributore di elementi di ventilazione industriale, ventilatori di trasporto, filtri, silos, cicloni, cabine insonorizzate e sistemi di otprasivanje (depolverazione). Attivo dal 1995. Fit diretto e forte col settore target. Email generica non reperita, lasciata vuota. [DUPLICATO — vedi anche: 2026-09-12_23_Croazia_Varazdinska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,7 +553,6 @@
           <t>AIRMAT d.o.o.</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Primorsko-goranska, Rijeka (Pehlin)</t>
@@ -619,7 +617,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SCARTATO - fuori target settoriale. Distributore certificato di componenti industriali generici (cuscinetti, cinghie/pulegge, elettromotori, tubi, gomma/plastica), commercio all'ingrosso non specializzato. Nessuna specializzazione in depolverazione/trattamento aria.</t>
+          <t>SCARTATO - fuori target settoriale. Distributore certificato di componenti industriali generici (cuscinetti, cinghie/pulegge, elettromotori, tubi, gomma/plastica), commercio all'ingrosso non specializzato. Nessuna specializzazione in depolverazione/trattamento aria. [DUPLICATO — vedi anche: 2026-09-08_19_Croazia_Sisacko-moslavacka_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -634,7 +632,6 @@
           <t>AK WRAP d.o.o.</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Primorsko-goranska, Rijeka</t>
@@ -645,8 +642,6 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>SCARTATO - nessun riscontro specifico nel settore. Solo scheda Kompass generica, nessuna fonte indipendente conferma l'attivita di 'air filtration equipment'; nessun sito web proprio, nessun contatto reperibile.</t>

--- a/output/2026-09-13_20_Croazia_Primorsko-goranska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-13_20_Croazia_Primorsko-goranska_Depolverazione_Trattamento_aria.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (14/09/2026)</t>
         </is>
       </c>
     </row>
